--- a/public/excel/product/Giá thép V.xlsx
+++ b/public/excel/product/Giá thép V.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép V 30 x 30 x 3 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép V 40 x 40 x 4 x 6m</t>
@@ -548,7 +554,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -609,7 +617,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>6</v>
@@ -630,12 +638,14 @@
         <v>132.19</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -696,7 +706,7 @@
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>6</v>
@@ -717,12 +727,14 @@
         <v>235.22</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -783,7 +795,7 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -804,12 +816,14 @@
         <v>225.5</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -870,7 +884,7 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>6</v>
@@ -891,12 +905,14 @@
         <v>296.455</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -957,7 +973,7 @@
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>6</v>
@@ -978,12 +994,14 @@
         <v>366.437</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1044,7 +1062,7 @@
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>6</v>
@@ -1065,12 +1083,14 @@
         <v>463.635</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1131,7 +1151,7 @@
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>6</v>
@@ -1152,12 +1172,14 @@
         <v>352.829</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1218,7 +1240,7 @@
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>6</v>
@@ -1239,12 +1261,14 @@
         <v>444.196</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1305,7 +1329,7 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>6</v>
@@ -1326,12 +1350,14 @@
         <v>468.495</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1392,7 +1418,7 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>6</v>
@@ -1413,12 +1439,14 @@
         <v>555.974</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -1479,7 +1507,7 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>12</v>
@@ -1491,21 +1519,23 @@
         <v>14.727</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1566,7 +1596,7 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>12</v>
@@ -1578,21 +1608,23 @@
         <v>14.727</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -1653,7 +1685,7 @@
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>12</v>
@@ -1665,21 +1697,23 @@
         <v>14.727</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1740,7 +1774,7 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>12</v>
@@ -1752,21 +1786,23 @@
         <v>14.727</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1827,7 +1863,7 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>12</v>
@@ -1839,21 +1875,23 @@
         <v>16.364</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1914,7 +1952,7 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>12</v>
@@ -1926,21 +1964,23 @@
         <v>16.364</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2001,7 +2041,7 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>12</v>
@@ -2013,21 +2053,23 @@
         <v>16.364</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J18" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2088,7 +2130,7 @@
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>12</v>
@@ -2100,21 +2142,23 @@
         <v>16.364</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2175,7 +2219,7 @@
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>12</v>
@@ -2187,21 +2231,23 @@
         <v>16.364</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J20" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2262,7 +2308,7 @@
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>12</v>
@@ -2274,21 +2320,23 @@
         <v>17</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2349,7 +2397,7 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>12</v>
@@ -2361,21 +2409,23 @@
         <v>17</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J22" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -2436,7 +2486,7 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>12</v>
@@ -2448,21 +2498,23 @@
         <v>17</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2523,7 +2575,7 @@
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>12</v>
@@ -2535,21 +2587,23 @@
         <v>17</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J24" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2610,7 +2664,7 @@
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>12</v>
@@ -2622,21 +2676,23 @@
         <v>17</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J25" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2697,7 +2753,7 @@
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>12</v>
@@ -2709,21 +2765,23 @@
         <v>17</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J26" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2784,7 +2842,7 @@
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>12</v>
@@ -2796,21 +2854,23 @@
         <v>17</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J27" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2871,7 +2931,7 @@
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>12</v>
@@ -2883,21 +2943,23 @@
         <v>17</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J28" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2958,7 +3020,7 @@
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>12</v>
@@ -2970,21 +3032,23 @@
         <v>17</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J29" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -3045,7 +3109,7 @@
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>12</v>
@@ -3057,21 +3121,23 @@
         <v>17</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -3132,7 +3198,7 @@
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>12</v>
@@ -3144,21 +3210,23 @@
         <v>17</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J31" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -3219,7 +3287,7 @@
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>12</v>
@@ -3231,21 +3299,23 @@
         <v>17</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -3306,7 +3376,7 @@
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>12</v>
@@ -3318,21 +3388,23 @@
         <v>17</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J33" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -3393,7 +3465,7 @@
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>12</v>
@@ -3405,21 +3477,23 @@
         <v>17</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>18.7</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J34" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
